--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2239_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2239_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9c55bf19ff3343e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R00fc6cff7af14c17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,156 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.2200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.4200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.7000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.9300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6180</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    120.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.2360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.3440</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    127.1430</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>13/08/2026</x:t>
         </x:is>
       </x:c>

--- a/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2239_completo.xlsx
+++ b/4996_Cuenca_Mantaro/_raw_reportes_xlsx/IDConfig_2239_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R00fc6cff7af14c17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1cd4d90cb6d94cc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,696 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    102.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    104.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.0900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.7900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.5100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.4600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     97.6900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.8700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.7500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    120.6700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.6600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.8600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.1400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    129.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.0700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.5700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.0400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    124.5000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.5200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    117.2400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.6800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    110.7200</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.1300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.2300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    111.9800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.3300</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.4400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.7800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    116.2100</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    112.4700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    115.6500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    114.1600</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    118.5500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>23:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    119.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
